--- a/artfynd/A 38961-2019 artfynd.xlsx
+++ b/artfynd/A 38961-2019 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 38961-2019 artfynd.xlsx
+++ b/artfynd/A 38961-2019 artfynd.xlsx
@@ -4583,7 +4583,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">

--- a/artfynd/A 38961-2019 artfynd.xlsx
+++ b/artfynd/A 38961-2019 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY38"/>
+  <dimension ref="A1:AY39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5189,6 +5189,130 @@
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>123948134</v>
+      </c>
+      <c r="B39" t="n">
+        <v>57670</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>102623</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Trädlärka</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Lullula arborea</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Söderviken öster, Forsmarks kkv, bron över kanalen, Upl</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>675300</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6700079</v>
+      </c>
+      <c r="S39" t="n">
+        <v>100</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Forsmark</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-04-10</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-04-10</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Mathias Andersson</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Mathias Andersson</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
